--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3736</v>
+        <v>3903</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>151</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>5046</v>
+        <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2274</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="62">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="J84" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>27</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3311</v>
+        <v>3315</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3903</v>
+        <v>4261</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2316</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>3</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>1</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="J84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>474</v>
+        <v>325</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="N136" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O136" s="6" t="n">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3315</v>
+        <v>3317</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,35 +2839,35 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>181</v>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>2</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4261</v>
+        <v>3231</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="K73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O114" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3317</v>
+        <v>3334</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3231</v>
+        <v>3900</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>42</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2590</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>252</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>2</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>244</v>
@@ -5683,10 +5683,10 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>15</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3334</v>
+        <v>2619</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3900</v>
+        <v>1804</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>252</v>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="L72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>244</v>
@@ -5683,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1650</v>
+        <v>1185</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2619</v>
+        <v>2286</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1804</v>
+        <v>632</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>5</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1184</v>
+        <v>1142</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>325</v>
+        <v>201</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>632</v>
+        <v>1278</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>169</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5220</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2586</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>230</v>
+        <v>154</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1278</v>
+        <v>4985</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>5220</v>
+        <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5614,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>33</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>4</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,11 +740,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
       </c>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4985</v>
+        <v>2546</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I39" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J39" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="K39" s="4" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2720</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         <v>25</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2289</v>
+        <v>2277</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2546</v>
+        <v>3032</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>4</v>
+        <v>508</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>5</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6733,40 +6733,40 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>7</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2277</v>
+        <v>2910</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3032</v>
+        <v>2455</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>284</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>268</v>
@@ -5683,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1189</v>
+        <v>1141</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2910</v>
+        <v>3222</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2455</v>
+        <v>511</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>3</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1142</v>
+        <v>1030</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6957,7 +6957,7 @@
         <v>27</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>5</v>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1141</v>
+        <v>1584</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>24</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2548</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>11</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>535</v>
+        <v>3584</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>218</v>
@@ -3226,7 +3226,7 @@
         <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>24</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2556</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>26</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3222</v>
+        <v>3211</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3584</v>
+        <v>3774</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>580</v>
+        <v>1102</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2732</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J72" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K72" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>331</v>
+        <v>222</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3774</v>
+        <v>2217</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,36 +3200,36 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C39" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1102</v>
+        <v>1325</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>8</v>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3211</v>
+        <v>3249</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2217</v>
+        <v>3859</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1325</v>
+        <v>1337</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2882</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>257</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>250</v>
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3249</v>
+        <v>1952</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3859</v>
+        <v>1796</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,36 +3200,36 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C39" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="I39" s="4" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>257</v>
@@ -5626,10 +5626,10 @@
         <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>250</v>
@@ -5683,10 +5683,10 @@
         <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1030</v>
+        <v>1390</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         <v>26</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1585</v>
+        <v>1477</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1952</v>
+        <v>2052</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1796</v>
+        <v>530</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>13</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1347</v>
+        <v>1334</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>62</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2756</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>10</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1390</v>
+        <v>1477</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>6</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2052</v>
+        <v>2074</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>530</v>
+        <v>3119</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>268</v>
@@ -3226,7 +3226,7 @@
         <v>138</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>62</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2614</v>
+        <v>2596</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2808</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>10</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6957,10 +6957,10 @@
         <v>26</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>28</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>111</v>
+        <v>336</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>6</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2074</v>
+        <v>2134</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3119</v>
+        <v>3602</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>138</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1329</v>
+        <v>1271</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2596</v>
+        <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2670</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>336</v>
+        <v>113</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,14 +9225,14 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C122" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D122" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O135" s="4" t="n">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3602</v>
+        <v>2614</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1271</v>
+        <v>1213</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>3</v>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,34 +5605,34 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>259</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="I72" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="J72" s="6" t="n">
-        <v>25</v>
-      </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,38 +5658,38 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>248</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="I73" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="J86" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,14 +9225,14 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D122" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C122" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D122" s="6" t="n">
-        <v>13</v>
-      </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2839,35 +2839,35 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2614</v>
+        <v>2666</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1213</v>
+        <v>1123</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2676</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>3</v>
       </c>
       <c r="C72" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>240</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>233</v>
@@ -5686,10 +5686,10 @@
         <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2133</v>
+        <v>754</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2666</v>
+        <v>1664</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1123</v>
+        <v>1137</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>10</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2578</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="62">
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>240</v>
@@ -5629,10 +5629,10 @@
         <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>233</v>
@@ -5683,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1477</v>
+        <v>881</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1505</v>
+        <v>29</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>337</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>754</v>
+        <v>139</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1664</v>
+        <v>807</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>12</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1137</v>
+        <v>1156</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>51</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2614</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2652</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>881</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>337</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>807</v>
+        <v>1614</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>324</v>
@@ -3223,10 +3223,10 @@
         <v>30</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>51</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2614</v>
+        <v>2610</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2664</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>339</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1614</v>
+        <v>4101</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1154</v>
+        <v>1068</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>2</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2610</v>
+        <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2502</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>2</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>339</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>3</v>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4101</v>
+        <v>1788</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1068</v>
+        <v>1033</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2508</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>311</v>
+        <v>223</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>2</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>3</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1788</v>
+        <v>1934</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1033</v>
+        <v>911</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2474</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="C72" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>5</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>258</v>
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6960,7 +6960,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>3</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1934</v>
+        <v>1251</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>38</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>911</v>
+        <v>977</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>273</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5683,10 +5683,10 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         <v>16</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>2</v>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1251</v>
+        <v>1922</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>21</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>977</v>
+        <v>1002</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>273</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>258</v>
@@ -5683,13 +5683,13 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6957,11 +6957,11 @@
         <v>16</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>114</v>
+        <v>344</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>0</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -767,7 +767,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1922</v>
+        <v>664</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1002</v>
+        <v>1064</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>4</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2510</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="62">
@@ -5611,10 +5611,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>21</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5683,13 +5683,13 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>664</v>
+        <v>594</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>341</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>32</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>30</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2460</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6960,28 +6960,28 @@
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>594</v>
+        <v>2611</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1085</v>
+        <v>1028</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>30</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5614,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,34 +6954,34 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1301,18 +1301,18 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>9</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2611</v>
+        <v>1513</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1028</v>
+        <v>780</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>30</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>4</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2508</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="62">
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>1</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>1</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>2</v>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>228</v>
+        <v>117</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1513</v>
+        <v>1690</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,36 +3200,36 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="E39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="I39" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>780</v>
+        <v>692</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2528</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,31 +5605,31 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="C72" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>306</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
         <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1690</v>
+        <v>2918</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>4</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>692</v>
+        <v>566</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>27</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -3583,10 +3583,10 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>299</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="I72" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>18</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>275</v>
@@ -5683,10 +5683,10 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>12</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3</v>
+        <v>1842</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2918</v>
+        <v>1661</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>4</v>
@@ -3226,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>566</v>
+        <v>486</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>204</v>
+        <v>89</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2472</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="L72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5680,22 +5680,22 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="K73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>12</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1842</v>
+        <v>1989</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1661</v>
+        <v>275</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>4</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>486</v>
+        <v>406</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>18</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>6</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1006</v>
+        <v>1183</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6957,10 +6957,10 @@
         <v>14</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>73</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2512</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>6</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1304,7 +1304,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>156</v>
+        <v>1156</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>3</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>18</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2508</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>6</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>0</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1156</v>
+        <v>1685</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,36 +3200,36 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I39" s="4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>414</v>
+        <v>722</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2550</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5686,10 +5686,10 @@
         <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,42 +6088,42 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,40 +6228,40 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>257</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>12</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>8</v>
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1685</v>
+        <v>1727</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>722</v>
+        <v>1014</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>3</v>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2602</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="62">
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>49</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>12</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,11 +740,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
       </c>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2016</v>
+        <v>2302</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1727</v>
+        <v>718</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1014</v>
+        <v>1042</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2544</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>290</v>
@@ -5626,19 +5626,19 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="L72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>280</v>
@@ -5683,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1184</v>
+        <v>657</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6954,34 +6954,34 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>217</v>
+        <v>1077</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2302</v>
+        <v>2866</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>718</v>
+        <v>178</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>33</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2614</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>9</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>657</v>
+        <v>1176</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>4</v>
@@ -6981,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>230</v>
+        <v>345</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>33</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>178</v>
+        <v>1917</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>2</v>
@@ -3226,7 +3226,7 @@
         <v>96</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>33</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>1</v>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2632</v>
+        <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>9</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1077</v>
+        <v>1099</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>345</v>
+        <v>115</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>33</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -767,16 +767,16 @@
         <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1917</v>
+        <v>2123</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,13 +3223,13 @@
         <v>7</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1044</v>
+        <v>1153</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2602</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="62">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="N62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>2</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>371</v>
+        <v>421</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
         <v>4</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>115</v>
+        <v>232</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2865</v>
+        <v>2891</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2123</v>
+        <v>4982</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1153</v>
+        <v>1113</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2538</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2891</v>
+        <v>2914</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4982</v>
+        <v>2140</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1113</v>
+        <v>1094</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>343</v>
@@ -5623,16 +5623,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="I72" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>321</v>
@@ -5680,16 +5680,16 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K73" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6954,34 +6954,34 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1099</v>
+        <v>1426</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2914</v>
+        <v>2152</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2140</v>
+        <v>426</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>20</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>1094</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>648</v>
+        <v>772</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="62">
@@ -5605,34 +5605,34 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>342</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>343</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5686,10 +5686,10 @@
         <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1175</v>
+        <v>1017</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6957,10 +6957,10 @@
         <v>36</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1426</v>
+        <v>1576</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>223</v>
+        <v>330</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>426</v>
+        <v>299</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1916</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>330</v>
+        <v>222</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>37</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2152</v>
+        <v>2134</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>299</v>
+        <v>3066</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>8</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>781</v>
+        <v>854</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1720</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="62">
@@ -5617,7 +5617,7 @@
         <v>341</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1576</v>
+        <v>1551</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>19</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>13</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2134</v>
+        <v>2157</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3066</v>
+        <v>3422</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I39" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="J39" s="4" t="n">
-        <v>1093</v>
+        <v>1023</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>854</v>
+        <v>1316</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1176</v>
+        <v>862</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>35</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>2</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>316</v>
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>3</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>2</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O114" s="6" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2157</v>
+        <v>2150</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3422</v>
+        <v>2254</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1023</v>
+        <v>1068</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>2</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1316</v>
+        <v>1336</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5629,10 +5629,10 @@
         <v>22</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,42 +6088,42 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,40 +6228,40 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D100" s="6" t="n">
         <v>19</v>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2254</v>
+        <v>2850</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1068</v>
+        <v>1113</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1336</v>
+        <v>1164</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>300</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
@@ -5683,13 +5683,13 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2165</v>
+        <v>3133</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2850</v>
+        <v>952</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1164</v>
+        <v>1033</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>300</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>288</v>
@@ -5680,16 +5680,16 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1017</v>
+        <v>458</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1550</v>
+        <v>1733</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>18</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3133</v>
+        <v>3698</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>952</v>
+        <v>87</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>23</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1033</v>
+        <v>1001</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>322</v>
+        <v>824</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>458</v>
+        <v>787</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6957,10 +6957,10 @@
         <v>25</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1733</v>
+        <v>1740</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>25</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3698</v>
+        <v>3675</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>87</v>
+        <v>2565</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>248</v>
@@ -3223,10 +3223,10 @@
         <v>11</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>1001</v>
+        <v>872</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>824</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>27</v>
@@ -5667,7 +5667,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>25</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2565</v>
+        <v>1571</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>3</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>872</v>
+        <v>513</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0</v>
+        <v>1946</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1684</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,42 +6088,42 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,40 +6228,40 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7643,7 @@
         <v>13</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,34 +9225,34 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D122" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="6" t="n">
-        <v>25</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2</v>
@@ -767,19 +767,19 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3675</v>
+        <v>3685</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1571</v>
+        <v>1811</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1064</v>
+        <v>1021</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>513</v>
+        <v>432</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1946</v>
+        <v>5264</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1932</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>542</v>
+        <v>354</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5664,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5686,10 +5686,10 @@
         <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>1</v>
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3685</v>
+        <v>3412</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1811</v>
+        <v>1181</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>11</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>264</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>3</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>246</v>
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>3</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,37 +6228,37 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>6</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>3</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1739</v>
+        <v>1938</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3412</v>
+        <v>2333</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>2</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>2</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1181</v>
+        <v>237</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>360</v>
+        <v>506</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5264</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="62">
@@ -5608,16 +5608,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>7</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>3</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>3</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>787</v>
+        <v>1117</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,37 +6228,37 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>6</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1938</v>
+        <v>1674</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="J101" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2333</v>
+        <v>2328</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5264</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2628</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5617,7 +5617,7 @@
         <v>256</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>6</v>
@@ -6957,10 +6957,10 @@
         <v>20</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1674</v>
+        <v>1665</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>339</v>
+        <v>224</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         <v>3</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>225</v>
+        <v>717</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5264</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>6</v>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>1</v>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>15</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>717</v>
+        <v>1561</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>6</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1070</v>
+        <v>1184</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>7</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>494</v>
+        <v>436</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>5264</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2616</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>0</v>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,13 +5683,13 @@
         <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6954,34 +6954,34 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>298</v>
+        <v>22</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O135" s="4" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="N136" s="6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O136" s="6" t="n">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="N19" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1561</v>
+        <v>6442</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1184</v>
+        <v>1168</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>14</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>5264</v>
+        <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="62">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>354</v>
+        <v>542</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -5605,19 +5605,19 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
         <v>2</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>8</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         <v>3</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,42 +6088,42 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>0</v>
@@ -6228,40 +6228,40 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K81" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>226</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2328</v>
+        <v>2290</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,35 +2839,35 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>6442</v>
+        <v>2821</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>283</v>
+        <v>326</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1168</v>
+        <v>1189</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>467</v>
+        <v>564</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>3</v>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2584</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="62">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>259</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>244</v>
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="H73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>3</v>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>8</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2290</v>
+        <v>400</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2821</v>
+        <v>828</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1189</v>
+        <v>1164</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>564</v>
+        <v>446</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>1</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>259</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>244</v>
@@ -5683,10 +5683,10 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>1</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>1117</v>
+        <v>186</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1669</v>
+        <v>8</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>400</v>
+        <v>48</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>828</v>
+        <v>203</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2580</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>2</v>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>112</v>
+        <v>336</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>205</v>
+        <v>532</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>203</v>
+        <v>1844</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>26</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>335</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>21</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="K41" s="4" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0</v>
+        <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2544</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="62">
@@ -5614,10 +5614,10 @@
         <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>336</v>
+        <v>224</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>8</v>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>

--- a/output/overall_report.xlsx
+++ b/output/overall_report.xlsx
@@ -743,37 +743,37 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>532</v>
+        <v>833</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>1</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1844</v>
+        <v>1909</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>1</v>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1159</v>
+        <v>1047</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>3</v>
@@ -4867,7 +4867,7 @@
         <v>2632</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2506</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="62">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>19</v>
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>1</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I102" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O114" s="6" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>8</v>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>22</v>
+        <v>329</v>
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O135" s="4" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="N136" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O136" s="6" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="J139" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
